--- a/FAITH RICARDO.xlsx
+++ b/FAITH RICARDO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon-6.0.0\www\GestionExpensas2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08C57EE-CD18-4986-B1BB-5EBA8FAAB022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285897FD-4C80-4B0D-A88B-04501BE1237D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="279">
   <si>
     <t xml:space="preserve">EDIFICIO TORRE FAITH </t>
   </si>
@@ -117,9 +117,6 @@
     <t>98-95</t>
   </si>
   <si>
-    <t>CARMEN LINO</t>
-  </si>
-  <si>
     <t>97-94</t>
   </si>
   <si>
@@ -582,9 +579,6 @@
     <t>BEYMAR CHUQUIMIA</t>
   </si>
   <si>
-    <t>CARMENSUSANA  LINO ARAMAYO</t>
-  </si>
-  <si>
     <t>PAOLA ZUBIETA CALVETY</t>
   </si>
   <si>
@@ -865,6 +859,9 @@
   </si>
   <si>
     <t>Planta 30</t>
+  </si>
+  <si>
+    <t>CARMEN SUSANA LINO ARAMAYO</t>
   </si>
 </sst>
 </file>
@@ -1563,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>13</v>
@@ -1617,10 +1614,10 @@
         <v>30</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -1649,10 +1646,10 @@
         <v>30</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -1684,7 +1681,7 @@
         <v>17</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -1716,7 +1713,7 @@
         <v>18</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -1745,10 +1742,10 @@
         <v>30</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1777,10 +1774,10 @@
         <v>30</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K17" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1812,7 +1809,7 @@
         <v>19</v>
       </c>
       <c r="K18" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1844,7 +1841,7 @@
         <v>20</v>
       </c>
       <c r="K19" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1876,7 +1873,7 @@
         <v>20</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1908,7 +1905,7 @@
         <v>21</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1940,7 +1937,7 @@
         <v>22</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1972,7 +1969,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -1984,7 +1981,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>14</v>
@@ -2001,10 +1998,10 @@
         <v>43.943999999999996</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2033,10 +2030,10 @@
         <v>30</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K25" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2065,10 +2062,10 @@
         <v>30</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K26" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2097,10 +2094,10 @@
         <v>87.455999999999989</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K27" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2132,7 +2129,7 @@
         <v>26</v>
       </c>
       <c r="K28" s="9" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2164,7 +2161,7 @@
         <v>28</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2193,10 +2190,10 @@
         <v>46.415999999999997</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>30</v>
+        <v>278</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2208,7 +2205,7 @@
         <v>24</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>14</v>
@@ -2225,10 +2222,10 @@
         <v>76.823999999999998</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -2257,10 +2254,10 @@
         <v>30</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -2289,10 +2286,10 @@
         <v>30</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -2321,10 +2318,10 @@
         <v>30</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -2333,7 +2330,7 @@
         <v>25</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D35" s="11">
         <v>93</v>
@@ -2353,10 +2350,10 @@
         <v>10.799999999999999</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -2365,7 +2362,7 @@
         <v>26</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36" s="20">
         <v>92</v>
@@ -2403,7 +2400,7 @@
         <v>27</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D37" s="11">
         <v>91</v>
@@ -2426,7 +2423,7 @@
         <v>17</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L37" s="26"/>
       <c r="M37" s="26"/>
@@ -2438,7 +2435,7 @@
         <v>28</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38" s="20">
         <v>90</v>
@@ -2476,7 +2473,7 @@
         <v>29</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D39" s="20">
         <v>89</v>
@@ -2514,7 +2511,7 @@
         <v>30</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D40" s="20">
         <v>88</v>
@@ -2552,7 +2549,7 @@
         <v>31</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41" s="11">
         <v>87</v>
@@ -2575,7 +2572,7 @@
         <v>20</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L41" s="26"/>
       <c r="M41" s="26"/>
@@ -2587,7 +2584,7 @@
         <v>32</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D42" s="11">
         <v>86</v>
@@ -2610,7 +2607,7 @@
         <v>22</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L42" s="26"/>
       <c r="M42" s="26"/>
@@ -2622,7 +2619,7 @@
         <v>33</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D43" s="11">
         <v>85</v>
@@ -2645,7 +2642,7 @@
         <v>21</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L43" s="26"/>
       <c r="M43" s="26"/>
@@ -2657,7 +2654,7 @@
         <v>34</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D44" s="11">
         <v>84</v>
@@ -2677,10 +2674,10 @@
         <v>14.735999999999999</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L44" s="26"/>
       <c r="M44" s="26"/>
@@ -2692,7 +2689,7 @@
         <v>35</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D45" s="11">
         <v>83</v>
@@ -2712,10 +2709,10 @@
         <v>13.272</v>
       </c>
       <c r="J45" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L45" s="28">
         <f t="shared" ref="L45:L67" si="3">+I45</f>
@@ -2730,7 +2727,7 @@
         <v>36</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D46" s="20">
         <v>82</v>
@@ -2768,7 +2765,7 @@
         <v>37</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D47" s="20">
         <v>81</v>
@@ -2806,7 +2803,7 @@
         <v>38</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D48" s="11">
         <v>80</v>
@@ -2826,10 +2823,10 @@
         <v>19.103999999999999</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L48" s="26"/>
       <c r="M48" s="26"/>
@@ -2841,7 +2838,7 @@
         <v>39</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" s="20">
         <v>79</v>
@@ -2879,7 +2876,7 @@
         <v>40</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D50" s="11">
         <v>78</v>
@@ -2899,10 +2896,10 @@
         <v>12.023999999999999</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L50" s="28">
         <f t="shared" si="3"/>
@@ -2917,7 +2914,7 @@
         <v>41</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D51" s="11">
         <v>77</v>
@@ -2937,10 +2934,10 @@
         <v>13.632</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L51" s="28"/>
       <c r="M51" s="26"/>
@@ -2952,7 +2949,7 @@
         <v>42</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D52" s="20">
         <v>75</v>
@@ -2990,7 +2987,7 @@
         <v>43</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D53" s="38">
         <v>74</v>
@@ -3010,10 +3007,10 @@
         <v>10.368</v>
       </c>
       <c r="J53" s="30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K53" s="31" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L53" s="23">
         <f t="shared" si="3"/>
@@ -3028,7 +3025,7 @@
         <v>44</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D54" s="20">
         <v>73</v>
@@ -3066,7 +3063,7 @@
         <v>45</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D55" s="20">
         <v>72</v>
@@ -3104,7 +3101,7 @@
         <v>46</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D56" s="11">
         <v>71</v>
@@ -3124,10 +3121,10 @@
         <v>17.28</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L56" s="26"/>
       <c r="M56" s="26"/>
@@ -3139,7 +3136,7 @@
         <v>47</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D57" s="20">
         <v>70</v>
@@ -3177,7 +3174,7 @@
         <v>48</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D58" s="20">
         <v>69</v>
@@ -3215,7 +3212,7 @@
         <v>49</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D59" s="11">
         <v>67</v>
@@ -3235,7 +3232,7 @@
         <v>21.84</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K59" s="9"/>
       <c r="L59" s="16">
@@ -3252,7 +3249,7 @@
         <v>50</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D60" s="20">
         <v>66</v>
@@ -3290,7 +3287,7 @@
         <v>51</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D61" s="20">
         <v>65</v>
@@ -3328,7 +3325,7 @@
         <v>52</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D62" s="20">
         <v>64</v>
@@ -3366,7 +3363,7 @@
         <v>53</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D63" s="20">
         <v>63</v>
@@ -3404,7 +3401,7 @@
         <v>54</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D64" s="11">
         <v>62</v>
@@ -3424,10 +3421,10 @@
         <v>20.544</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L64" s="26"/>
       <c r="M64" s="26"/>
@@ -3439,7 +3436,7 @@
         <v>55</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D65" s="20">
         <v>61</v>
@@ -3477,7 +3474,7 @@
         <v>56</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D66" s="20">
         <v>60</v>
@@ -3515,7 +3512,7 @@
         <v>57</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D67" s="20">
         <v>59</v>
@@ -3553,7 +3550,7 @@
         <v>58</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D68" s="11">
         <v>58</v>
@@ -3576,7 +3573,7 @@
         <v>18</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L68" s="26"/>
       <c r="M68" s="26"/>
@@ -3594,7 +3591,7 @@
         <v>93</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F69" s="12">
         <v>12.5</v>
@@ -3608,10 +3605,10 @@
         <v>30</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L69" s="26"/>
       <c r="M69" s="26"/>
@@ -3629,7 +3626,7 @@
         <v>92</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F70" s="12">
         <v>12.5</v>
@@ -3643,10 +3640,10 @@
         <v>30</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L70" s="26"/>
       <c r="M70" s="26"/>
@@ -3664,7 +3661,7 @@
         <v>91</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F71" s="12">
         <v>12.5</v>
@@ -3678,10 +3675,10 @@
         <v>30</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L71" s="26"/>
       <c r="M71" s="26"/>
@@ -3699,7 +3696,7 @@
         <v>90</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F72" s="12">
         <v>12.5</v>
@@ -3713,10 +3710,10 @@
         <v>30</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L72" s="26"/>
       <c r="M72" s="26"/>
@@ -3734,7 +3731,7 @@
         <v>89</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F73" s="12">
         <v>12.5</v>
@@ -3748,10 +3745,10 @@
         <v>30</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L73" s="26"/>
       <c r="M73" s="26"/>
@@ -3769,7 +3766,7 @@
         <v>88</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F74" s="12">
         <v>12.5</v>
@@ -3783,10 +3780,10 @@
         <v>30</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L74" s="26"/>
       <c r="M74" s="26"/>
@@ -3804,7 +3801,7 @@
         <v>87</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F75" s="12">
         <v>12.5</v>
@@ -3818,10 +3815,10 @@
         <v>30</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L75" s="26"/>
       <c r="M75" s="26"/>
@@ -3839,7 +3836,7 @@
         <v>86</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F76" s="12">
         <v>12.5</v>
@@ -3853,10 +3850,10 @@
         <v>30</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L76" s="26"/>
       <c r="M76" s="26"/>
@@ -3874,7 +3871,7 @@
         <v>85</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F77" s="12">
         <v>12.5</v>
@@ -3888,10 +3885,10 @@
         <v>30</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L77" s="26"/>
       <c r="M77" s="26"/>
@@ -3909,7 +3906,7 @@
         <v>84</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F78" s="12">
         <v>12.5</v>
@@ -3923,10 +3920,10 @@
         <v>30</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L78" s="26"/>
       <c r="M78" s="26"/>
@@ -3944,7 +3941,7 @@
         <v>83</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F79" s="12">
         <v>12.5</v>
@@ -3958,10 +3955,10 @@
         <v>30</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L79" s="26"/>
       <c r="M79" s="26"/>
@@ -3979,7 +3976,7 @@
         <v>82</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F80" s="32">
         <v>12.5</v>
@@ -3993,10 +3990,10 @@
         <v>30</v>
       </c>
       <c r="J80" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K80" s="34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="L80" s="35">
         <f t="shared" ref="L80" si="6">+I80</f>
@@ -4017,7 +4014,7 @@
         <v>81</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F81" s="12">
         <v>12.5</v>
@@ -4031,10 +4028,10 @@
         <v>30</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="L81" s="26"/>
       <c r="M81" s="26"/>
@@ -4052,7 +4049,7 @@
         <v>80</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F82" s="12">
         <v>25</v>
@@ -4066,10 +4063,10 @@
         <v>60</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L82" s="26"/>
       <c r="M82" s="26"/>
@@ -4087,7 +4084,7 @@
         <v>79</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F83" s="12">
         <v>12.5</v>
@@ -4101,10 +4098,10 @@
         <v>30</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L83" s="26"/>
       <c r="M83" s="26"/>
@@ -4122,7 +4119,7 @@
         <v>78</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F84" s="12">
         <v>12.5</v>
@@ -4136,10 +4133,10 @@
         <v>30</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L84" s="26"/>
       <c r="M84" s="26"/>
@@ -4157,7 +4154,7 @@
         <v>77</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F85" s="12">
         <v>12.5</v>
@@ -4171,10 +4168,10 @@
         <v>30</v>
       </c>
       <c r="J85" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L85" s="26"/>
       <c r="M85" s="26"/>
@@ -4192,7 +4189,7 @@
         <v>76</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F86" s="12">
         <v>12.5</v>
@@ -4206,10 +4203,10 @@
         <v>30</v>
       </c>
       <c r="J86" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L86" s="26"/>
       <c r="M86" s="26"/>
@@ -4227,7 +4224,7 @@
         <v>75</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F87" s="12">
         <v>12.5</v>
@@ -4241,10 +4238,10 @@
         <v>30</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K87" s="13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L87" s="26"/>
       <c r="M87" s="26"/>
@@ -4262,7 +4259,7 @@
         <v>74</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F88" s="12">
         <v>12.5</v>
@@ -4276,10 +4273,10 @@
         <v>30</v>
       </c>
       <c r="J88" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K88" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L88" s="26"/>
       <c r="M88" s="26"/>
@@ -4294,10 +4291,10 @@
         <v>24</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F89" s="12">
         <v>24.1</v>
@@ -4311,10 +4308,10 @@
         <v>57.84</v>
       </c>
       <c r="J89" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L89" s="26"/>
       <c r="M89" s="26"/>
@@ -4332,7 +4329,7 @@
         <v>72</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F90" s="12">
         <v>12.5</v>
@@ -4346,10 +4343,10 @@
         <v>30</v>
       </c>
       <c r="J90" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="L90" s="26"/>
       <c r="M90" s="26"/>
@@ -4367,7 +4364,7 @@
         <v>71</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F91" s="12">
         <v>12.5</v>
@@ -4381,10 +4378,10 @@
         <v>30</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K91" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L91" s="26"/>
       <c r="M91" s="26"/>
@@ -4402,7 +4399,7 @@
         <v>70</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F92" s="12">
         <v>12.5</v>
@@ -4416,10 +4413,10 @@
         <v>30</v>
       </c>
       <c r="J92" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K92" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L92" s="26"/>
       <c r="M92" s="26"/>
@@ -4437,7 +4434,7 @@
         <v>69</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F93" s="12">
         <v>12.5</v>
@@ -4451,10 +4448,10 @@
         <v>30</v>
       </c>
       <c r="J93" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K93" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L93" s="26"/>
       <c r="M93" s="26"/>
@@ -4472,7 +4469,7 @@
         <v>68</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F94" s="12">
         <v>12.5</v>
@@ -4486,10 +4483,10 @@
         <v>30</v>
       </c>
       <c r="J94" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K94" s="13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L94" s="26"/>
       <c r="M94" s="26"/>
@@ -4507,7 +4504,7 @@
         <v>67</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F95" s="12">
         <v>12.5</v>
@@ -4521,10 +4518,10 @@
         <v>30</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K95" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L95" s="26"/>
       <c r="M95" s="26"/>
@@ -4542,7 +4539,7 @@
         <v>66</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F96" s="12">
         <v>12.5</v>
@@ -4556,10 +4553,10 @@
         <v>30</v>
       </c>
       <c r="J96" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K96" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L96" s="26"/>
       <c r="M96" s="26"/>
@@ -4577,7 +4574,7 @@
         <v>65</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F97" s="12">
         <v>12.5</v>
@@ -4591,10 +4588,10 @@
         <v>30</v>
       </c>
       <c r="J97" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K97" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L97" s="26"/>
       <c r="M97" s="26"/>
@@ -4612,7 +4609,7 @@
         <v>64</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F98" s="12">
         <v>12.5</v>
@@ -4626,10 +4623,10 @@
         <v>30</v>
       </c>
       <c r="J98" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K98" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="L98" s="26"/>
       <c r="M98" s="26"/>
@@ -4647,7 +4644,7 @@
         <v>63</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F99" s="12">
         <v>12.5</v>
@@ -4661,10 +4658,10 @@
         <v>30</v>
       </c>
       <c r="J99" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K99" s="13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L99" s="26"/>
       <c r="M99" s="26"/>
@@ -4676,13 +4673,13 @@
         <v>90</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D100" s="11">
         <v>56</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F100" s="12">
         <v>5.57</v>
@@ -4696,10 +4693,10 @@
         <v>13.368</v>
       </c>
       <c r="J100" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K100" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
@@ -4711,13 +4708,13 @@
         <v>91</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D101" s="11">
         <v>55</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F101" s="12">
         <v>5.57</v>
@@ -4731,10 +4728,10 @@
         <v>13.368</v>
       </c>
       <c r="J101" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="K101" s="13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L101" s="26"/>
       <c r="M101" s="26"/>
@@ -4746,13 +4743,13 @@
         <v>92</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D102" s="11">
         <v>54</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F102" s="12">
         <v>5.57</v>
@@ -4766,10 +4763,10 @@
         <v>13.368</v>
       </c>
       <c r="J102" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K102" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L102" s="28">
         <f t="shared" ref="L102" si="7">+I102</f>
@@ -4784,13 +4781,13 @@
         <v>93</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D103" s="11">
         <v>53</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F103" s="12">
         <v>5.57</v>
@@ -4804,10 +4801,10 @@
         <v>13.368</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L103" s="26"/>
       <c r="M103" s="26"/>
@@ -4819,13 +4816,13 @@
         <v>94</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D104" s="11">
         <v>52</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F104" s="12">
         <v>5.51</v>
@@ -4839,10 +4836,10 @@
         <v>13.223999999999998</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L104" s="26"/>
       <c r="M104" s="26"/>
@@ -4854,13 +4851,13 @@
         <v>95</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D105" s="11">
         <v>51</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F105" s="12">
         <v>5.62</v>
@@ -4874,10 +4871,10 @@
         <v>13.488</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L105" s="26"/>
       <c r="M105" s="26"/>
@@ -4889,13 +4886,13 @@
         <v>96</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D106" s="11">
         <v>50</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F106" s="12">
         <v>5.57</v>
@@ -4909,10 +4906,10 @@
         <v>13.368</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="L106" s="26"/>
       <c r="M106" s="26"/>
@@ -4924,13 +4921,13 @@
         <v>97</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D107" s="11">
         <v>49</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F107" s="12">
         <v>5.57</v>
@@ -4944,10 +4941,10 @@
         <v>13.368</v>
       </c>
       <c r="J107" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
@@ -4959,13 +4956,13 @@
         <v>98</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D108" s="11">
         <v>48</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F108" s="12">
         <v>5.57</v>
@@ -4979,10 +4976,10 @@
         <v>13.368</v>
       </c>
       <c r="J108" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
@@ -4994,13 +4991,13 @@
         <v>99</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D109" s="11">
         <v>47</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F109" s="12">
         <v>5.51</v>
@@ -5014,10 +5011,10 @@
         <v>13.223999999999998</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K109" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
@@ -5029,13 +5026,13 @@
         <v>100</v>
       </c>
       <c r="C110" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D110" s="20">
         <v>46</v>
       </c>
       <c r="E110" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F110" s="21">
         <v>5.57</v>
@@ -5052,7 +5049,7 @@
         <v>15</v>
       </c>
       <c r="K110" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L110" s="23">
         <f t="shared" ref="L110:L115" si="8">+I110</f>
@@ -5067,13 +5064,13 @@
         <v>101</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D111" s="20">
         <v>45</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F111" s="21">
         <v>18.78</v>
@@ -5090,7 +5087,7 @@
         <v>15</v>
       </c>
       <c r="K111" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L111" s="23">
         <f t="shared" si="8"/>
@@ -5105,13 +5102,13 @@
         <v>102</v>
       </c>
       <c r="C112" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D112" s="20">
         <v>44</v>
       </c>
       <c r="E112" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F112" s="21">
         <v>7.38</v>
@@ -5128,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="K112" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L112" s="23">
         <f t="shared" si="8"/>
@@ -5143,13 +5140,13 @@
         <v>103</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D113" s="11">
         <v>43</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F113" s="12">
         <v>7.62</v>
@@ -5163,10 +5160,10 @@
         <v>18.288</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L113" s="26"/>
       <c r="M113" s="26"/>
@@ -5178,13 +5175,13 @@
         <v>104</v>
       </c>
       <c r="C114" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D114" s="20">
         <v>42</v>
       </c>
       <c r="E114" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F114" s="21">
         <v>7.62</v>
@@ -5201,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="K114" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L114" s="23">
         <f t="shared" si="8"/>
@@ -5216,13 +5213,13 @@
         <v>105</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D115" s="20">
         <v>301</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F115" s="21">
         <v>10.67</v>
@@ -5239,7 +5236,7 @@
         <v>15</v>
       </c>
       <c r="K115" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L115" s="23">
         <f t="shared" si="8"/>
@@ -5254,13 +5251,13 @@
         <v>106</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D116" s="11">
         <v>40</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F116" s="12">
         <v>5.52</v>
@@ -5274,10 +5271,10 @@
         <v>13.247999999999999</v>
       </c>
       <c r="J116" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L116" s="26"/>
       <c r="M116" s="26"/>
@@ -5289,13 +5286,13 @@
         <v>107</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D117" s="11">
         <v>41</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F117" s="12">
         <v>5.62</v>
@@ -5309,10 +5306,10 @@
         <v>13.488</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L117" s="26"/>
       <c r="M117" s="26"/>
@@ -5330,7 +5327,7 @@
         <v>62</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F118" s="12">
         <v>12.5</v>
@@ -5344,10 +5341,10 @@
         <v>30</v>
       </c>
       <c r="J118" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L118" s="26"/>
       <c r="M118" s="26"/>
@@ -5365,7 +5362,7 @@
         <v>61</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F119" s="12">
         <v>12.5</v>
@@ -5379,10 +5376,10 @@
         <v>30</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="L119" s="26"/>
       <c r="M119" s="26"/>
@@ -5400,7 +5397,7 @@
         <v>60</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F120" s="12">
         <v>12.5</v>
@@ -5414,10 +5411,10 @@
         <v>30</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L120" s="26"/>
       <c r="M120" s="26"/>
@@ -5435,7 +5432,7 @@
         <v>59</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F121" s="12">
         <v>12.5</v>
@@ -5449,10 +5446,10 @@
         <v>30</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L121" s="26"/>
       <c r="M121" s="26"/>
@@ -5470,7 +5467,7 @@
         <v>58</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F122" s="12">
         <v>12.5</v>
@@ -5484,10 +5481,10 @@
         <v>30</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K122" s="13" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L122" s="26"/>
       <c r="M122" s="26"/>
@@ -5505,7 +5502,7 @@
         <v>57</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F123" s="12">
         <v>12.5</v>
@@ -5519,10 +5516,10 @@
         <v>30</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L123" s="26"/>
       <c r="M123" s="26"/>
@@ -5540,7 +5537,7 @@
         <v>56</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F124" s="12">
         <v>12.5</v>
@@ -5554,10 +5551,10 @@
         <v>30</v>
       </c>
       <c r="J124" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="L124" s="26"/>
       <c r="M124" s="26"/>
@@ -5575,7 +5572,7 @@
         <v>55</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F125" s="12">
         <v>12.5</v>
@@ -5589,10 +5586,10 @@
         <v>30</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L125" s="26"/>
       <c r="M125" s="26"/>
@@ -5610,7 +5607,7 @@
         <v>54</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F126" s="12">
         <v>12.5</v>
@@ -5624,10 +5621,10 @@
         <v>30</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L126" s="26"/>
       <c r="M126" s="26"/>
@@ -5645,7 +5642,7 @@
         <v>53</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F127" s="12">
         <v>12.5</v>
@@ -5659,10 +5656,10 @@
         <v>30</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L127" s="26"/>
       <c r="M127" s="26"/>
@@ -5680,7 +5677,7 @@
         <v>52</v>
       </c>
       <c r="E128" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F128" s="12">
         <v>12.5</v>
@@ -5694,10 +5691,10 @@
         <v>30</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K128" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L128" s="26"/>
       <c r="M128" s="26"/>
@@ -5715,7 +5712,7 @@
         <v>51</v>
       </c>
       <c r="E129" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F129" s="12">
         <v>12.5</v>
@@ -5729,10 +5726,10 @@
         <v>30</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L129" s="26"/>
       <c r="M129" s="26"/>
@@ -5750,7 +5747,7 @@
         <v>50</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F130" s="12">
         <v>12.5</v>
@@ -5764,10 +5761,10 @@
         <v>30</v>
       </c>
       <c r="J130" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K130" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L130" s="26"/>
       <c r="M130" s="26"/>
@@ -5785,7 +5782,7 @@
         <v>49</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F131" s="12">
         <v>12.5</v>
@@ -5799,10 +5796,10 @@
         <v>30</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -5817,7 +5814,7 @@
         <v>48</v>
       </c>
       <c r="E132" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F132" s="12">
         <v>12.5</v>
@@ -5831,10 +5828,10 @@
         <v>30</v>
       </c>
       <c r="J132" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K132" s="9" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -5849,7 +5846,7 @@
         <v>47</v>
       </c>
       <c r="E133" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F133" s="12">
         <v>12.5</v>
@@ -5863,10 +5860,10 @@
         <v>30</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K133" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="134" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -5881,7 +5878,7 @@
         <v>46</v>
       </c>
       <c r="E134" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F134" s="12">
         <v>12.5</v>
@@ -5895,10 +5892,10 @@
         <v>30</v>
       </c>
       <c r="J134" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K134" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="135" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -5913,7 +5910,7 @@
         <v>45</v>
       </c>
       <c r="E135" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F135" s="12">
         <v>12.5</v>
@@ -5927,10 +5924,10 @@
         <v>30</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K135" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="136" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -5945,7 +5942,7 @@
         <v>44</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F136" s="12">
         <v>12.5</v>
@@ -5959,10 +5956,10 @@
         <v>30</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K136" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="137" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -5974,10 +5971,10 @@
         <v>24</v>
       </c>
       <c r="D137" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F137" s="12">
         <v>20.27</v>
@@ -5991,10 +5988,10 @@
         <v>48.647999999999996</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K137" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="138" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6006,10 +6003,10 @@
         <v>24</v>
       </c>
       <c r="D138" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E138" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F138" s="12">
         <v>20.61</v>
@@ -6023,10 +6020,10 @@
         <v>49.463999999999999</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K138" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="139" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6038,10 +6035,10 @@
         <v>24</v>
       </c>
       <c r="D139" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E139" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F139" s="12">
         <v>20.399999999999999</v>
@@ -6055,10 +6052,10 @@
         <v>48.959999999999994</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K139" s="17" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L139" s="16">
         <f t="shared" ref="L139" si="10">+I139</f>
@@ -6074,10 +6071,10 @@
         <v>24</v>
       </c>
       <c r="D140" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E140" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F140" s="12">
         <v>20.67</v>
@@ -6091,10 +6088,10 @@
         <v>49.608000000000004</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K140" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6106,10 +6103,10 @@
         <v>24</v>
       </c>
       <c r="D141" s="20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F141" s="21">
         <v>23.39</v>
@@ -6123,10 +6120,10 @@
         <v>56.136000000000003</v>
       </c>
       <c r="J141" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K141" s="18" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L141" s="23">
         <f>+I141</f>
@@ -6147,7 +6144,7 @@
         <v>38</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F142" s="12">
         <v>12.5</v>
@@ -6161,10 +6158,10 @@
         <v>30</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K142" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="143" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6179,7 +6176,7 @@
         <v>37</v>
       </c>
       <c r="E143" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F143" s="21">
         <v>12.5</v>
@@ -6193,10 +6190,10 @@
         <v>30</v>
       </c>
       <c r="J143" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K143" s="18" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L143" s="23">
         <f>+I143</f>
@@ -6217,7 +6214,7 @@
         <v>36</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F144" s="12">
         <v>25</v>
@@ -6231,10 +6228,10 @@
         <v>60</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K144" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="145" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6249,7 +6246,7 @@
         <v>35</v>
       </c>
       <c r="E145" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F145" s="12">
         <v>12.5</v>
@@ -6263,10 +6260,10 @@
         <v>30</v>
       </c>
       <c r="J145" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K145" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L145" s="23">
         <f t="shared" ref="L145" si="12">+I145</f>
@@ -6287,7 +6284,7 @@
         <v>34</v>
       </c>
       <c r="E146" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F146" s="12">
         <v>12.5</v>
@@ -6301,10 +6298,10 @@
         <v>30</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K146" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="147" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6319,7 +6316,7 @@
         <v>33</v>
       </c>
       <c r="E147" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F147" s="12">
         <v>12.5</v>
@@ -6333,10 +6330,10 @@
         <v>30</v>
       </c>
       <c r="J147" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K147" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6351,7 +6348,7 @@
         <v>32</v>
       </c>
       <c r="E148" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F148" s="12">
         <v>12.5</v>
@@ -6365,10 +6362,10 @@
         <v>30</v>
       </c>
       <c r="J148" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K148" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="149" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6377,13 +6374,13 @@
         <v>139</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D149" s="20">
         <v>39</v>
       </c>
       <c r="E149" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F149" s="21">
         <v>5.91</v>
@@ -6400,7 +6397,7 @@
         <v>15</v>
       </c>
       <c r="K149" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L149" s="23">
         <f t="shared" ref="L149:L152" si="13">+I149</f>
@@ -6415,13 +6412,13 @@
         <v>140</v>
       </c>
       <c r="C150" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D150" s="20">
         <v>38</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F150" s="21">
         <v>5.8</v>
@@ -6438,7 +6435,7 @@
         <v>15</v>
       </c>
       <c r="K150" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L150" s="23">
         <f t="shared" si="13"/>
@@ -6453,13 +6450,13 @@
         <v>141</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D151" s="20">
         <v>37</v>
       </c>
       <c r="E151" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F151" s="21">
         <v>21.17</v>
@@ -6476,7 +6473,7 @@
         <v>15</v>
       </c>
       <c r="K151" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L151" s="23">
         <f t="shared" si="13"/>
@@ -6491,13 +6488,13 @@
         <v>142</v>
       </c>
       <c r="C152" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D152" s="20">
         <v>36</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F152" s="21">
         <v>5.27</v>
@@ -6514,7 +6511,7 @@
         <v>15</v>
       </c>
       <c r="K152" s="22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L152" s="23">
         <f t="shared" si="13"/>
@@ -6529,13 +6526,13 @@
         <v>143</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D153" s="11">
         <v>35</v>
       </c>
       <c r="E153" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F153" s="12">
         <v>4.82</v>
@@ -6549,10 +6546,10 @@
         <v>11.568</v>
       </c>
       <c r="J153" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K153" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="154" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6561,13 +6558,13 @@
         <v>144</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D154" s="11">
         <v>34</v>
       </c>
       <c r="E154" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F154" s="12">
         <v>4.74</v>
@@ -6581,10 +6578,10 @@
         <v>11.375999999999999</v>
       </c>
       <c r="J154" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K154" s="9" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="155" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6593,13 +6590,13 @@
         <v>145</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D155" s="11">
         <v>33</v>
       </c>
       <c r="E155" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F155" s="12">
         <v>4.32</v>
@@ -6613,10 +6610,10 @@
         <v>10.368</v>
       </c>
       <c r="J155" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K155" s="9" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="156" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6625,13 +6622,13 @@
         <v>146</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D156" s="11">
         <v>32</v>
       </c>
       <c r="E156" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F156" s="12">
         <v>4.74</v>
@@ -6645,10 +6642,10 @@
         <v>11.375999999999999</v>
       </c>
       <c r="J156" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K156" s="9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="157" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6657,13 +6654,13 @@
         <v>147</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D157" s="20">
         <v>31</v>
       </c>
       <c r="E157" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F157" s="21">
         <v>4.32</v>
@@ -6695,13 +6692,13 @@
         <v>148</v>
       </c>
       <c r="C158" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D158" s="20">
         <v>30</v>
       </c>
       <c r="E158" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F158" s="21">
         <v>5.34</v>
@@ -6733,13 +6730,13 @@
         <v>149</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D159" s="11">
         <v>29</v>
       </c>
       <c r="E159" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F159" s="12">
         <v>4.7</v>
@@ -6753,10 +6750,10 @@
         <v>11.28</v>
       </c>
       <c r="J159" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K159" s="9" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="160" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6765,13 +6762,13 @@
         <v>150</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D160" s="11">
         <v>28</v>
       </c>
       <c r="E160" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F160" s="12">
         <v>7.8</v>
@@ -6785,10 +6782,10 @@
         <v>18.72</v>
       </c>
       <c r="J160" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K160" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="161" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6797,13 +6794,13 @@
         <v>151</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D161" s="11">
         <v>27</v>
       </c>
       <c r="E161" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F161" s="12">
         <v>9.2799999999999994</v>
@@ -6817,10 +6814,10 @@
         <v>22.271999999999998</v>
       </c>
       <c r="J161" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K161" s="9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="162" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -6829,13 +6826,13 @@
         <v>152</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D162" s="11">
         <v>26</v>
       </c>
       <c r="E162" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F162" s="12">
         <v>4.1500000000000004</v>
@@ -6849,10 +6846,10 @@
         <v>9.9600000000000009</v>
       </c>
       <c r="J162" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K162" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6861,13 +6858,13 @@
         <v>153</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D163" s="11">
         <v>25</v>
       </c>
       <c r="E163" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F163" s="12">
         <v>4.76</v>
@@ -6881,10 +6878,10 @@
         <v>11.423999999999999</v>
       </c>
       <c r="J163" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K163" s="9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="L163" s="23">
         <f t="shared" ref="L163:L165" si="15">+I163</f>
@@ -6899,13 +6896,13 @@
         <v>154</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D164" s="11">
         <v>24</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F164" s="12">
         <v>4.03</v>
@@ -6919,10 +6916,10 @@
         <v>9.6720000000000006</v>
       </c>
       <c r="J164" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K164" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="165" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -6931,13 +6928,13 @@
         <v>155</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D165" s="20">
         <v>23</v>
       </c>
       <c r="E165" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F165" s="21">
         <v>4.1900000000000004</v>
@@ -6969,13 +6966,13 @@
         <v>156</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D166" s="11">
         <v>22</v>
       </c>
       <c r="E166" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F166" s="12">
         <v>4.88</v>
@@ -6989,10 +6986,10 @@
         <v>11.712</v>
       </c>
       <c r="J166" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K166" s="9" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="167" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7001,13 +6998,13 @@
         <v>157</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D167" s="11">
         <v>21</v>
       </c>
       <c r="E167" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F167" s="12">
         <v>4.7</v>
@@ -7021,10 +7018,10 @@
         <v>11.28</v>
       </c>
       <c r="J167" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K167" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7033,13 +7030,13 @@
         <v>158</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D168" s="11">
         <v>20</v>
       </c>
       <c r="E168" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F168" s="12">
         <v>6.13</v>
@@ -7053,10 +7050,10 @@
         <v>14.712</v>
       </c>
       <c r="J168" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K168" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7065,13 +7062,13 @@
         <v>159</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D169" s="11">
         <v>19</v>
       </c>
       <c r="E169" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F169" s="12">
         <v>5.51</v>
@@ -7085,10 +7082,10 @@
         <v>13.223999999999998</v>
       </c>
       <c r="J169" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K169" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="170" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7097,13 +7094,13 @@
         <v>160</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D170" s="11">
         <v>18</v>
       </c>
       <c r="E170" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F170" s="12">
         <v>5.5</v>
@@ -7117,10 +7114,10 @@
         <v>13.2</v>
       </c>
       <c r="J170" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K170" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="171" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7129,13 +7126,13 @@
         <v>161</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D171" s="11">
         <v>17</v>
       </c>
       <c r="E171" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F171" s="12">
         <v>5.49</v>
@@ -7149,10 +7146,10 @@
         <v>13.176</v>
       </c>
       <c r="J171" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K171" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="172" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7161,13 +7158,13 @@
         <v>162</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D172" s="11">
         <v>16</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F172" s="12">
         <v>5.84</v>
@@ -7181,10 +7178,10 @@
         <v>14.016</v>
       </c>
       <c r="J172" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K172" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="173" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7193,13 +7190,13 @@
         <v>163</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D173" s="11">
         <v>10</v>
       </c>
       <c r="E173" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F173" s="12">
         <v>9.35</v>
@@ -7213,10 +7210,10 @@
         <v>22.439999999999998</v>
       </c>
       <c r="J173" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K173" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="174" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -7231,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F174" s="20">
         <v>325</v>
@@ -7265,13 +7262,13 @@
         <v>165</v>
       </c>
       <c r="C175" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D175" s="58">
         <v>1</v>
       </c>
       <c r="E175" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F175" s="58">
         <v>18.25</v>
@@ -7285,10 +7282,10 @@
         <v>76.650000000000006</v>
       </c>
       <c r="J175" s="61" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K175" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="176" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7297,13 +7294,13 @@
         <v>166</v>
       </c>
       <c r="C176" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D176" s="58">
         <v>2</v>
       </c>
       <c r="E176" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F176" s="59">
         <v>19.920000000000002</v>
@@ -7317,10 +7314,10 @@
         <v>83.664000000000016</v>
       </c>
       <c r="J176" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K176" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="177" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7329,13 +7326,13 @@
         <v>167</v>
       </c>
       <c r="C177" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D177" s="58">
         <v>3</v>
       </c>
       <c r="E177" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F177" s="59">
         <v>29.09</v>
@@ -7349,10 +7346,10 @@
         <v>122.17800000000001</v>
       </c>
       <c r="J177" s="61" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K177" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="178" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7361,13 +7358,13 @@
         <v>168</v>
       </c>
       <c r="C178" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D178" s="58">
         <v>4</v>
       </c>
       <c r="E178" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F178" s="59">
         <v>28.84</v>
@@ -7381,10 +7378,10 @@
         <v>121.128</v>
       </c>
       <c r="J178" s="61" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K178" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="179" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7393,13 +7390,13 @@
         <v>169</v>
       </c>
       <c r="C179" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D179" s="58">
         <v>5</v>
       </c>
       <c r="E179" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F179" s="59">
         <v>28.82</v>
@@ -7413,10 +7410,10 @@
         <v>121.04400000000001</v>
       </c>
       <c r="J179" s="61" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K179" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="180" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7425,13 +7422,13 @@
         <v>170</v>
       </c>
       <c r="C180" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D180" s="58">
         <v>6</v>
       </c>
       <c r="E180" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F180" s="59">
         <v>30.77</v>
@@ -7445,10 +7442,10 @@
         <v>129.23400000000001</v>
       </c>
       <c r="J180" s="61" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K180" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="181" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7457,13 +7454,13 @@
         <v>171</v>
       </c>
       <c r="C181" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D181" s="58">
         <v>7</v>
       </c>
       <c r="E181" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F181" s="59">
         <v>21.13</v>
@@ -7477,10 +7474,10 @@
         <v>88.745999999999995</v>
       </c>
       <c r="J181" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K181" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="182" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7489,13 +7486,13 @@
         <v>172</v>
       </c>
       <c r="C182" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D182" s="58">
         <v>8</v>
       </c>
       <c r="E182" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F182" s="59">
         <v>19.37</v>
@@ -7509,10 +7506,10 @@
         <v>81.354000000000013</v>
       </c>
       <c r="J182" s="61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K182" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="183" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7521,13 +7518,13 @@
         <v>173</v>
       </c>
       <c r="C183" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D183" s="58">
         <v>9</v>
       </c>
       <c r="E183" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F183" s="59">
         <v>21.44</v>
@@ -7541,10 +7538,10 @@
         <v>90.048000000000016</v>
       </c>
       <c r="J183" s="61" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K183" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="184" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7553,13 +7550,13 @@
         <v>174</v>
       </c>
       <c r="C184" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D184" s="58">
         <v>10</v>
       </c>
       <c r="E184" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F184" s="59">
         <v>23.35</v>
@@ -7573,10 +7570,10 @@
         <v>98.070000000000007</v>
       </c>
       <c r="J184" s="61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K184" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="185" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7585,13 +7582,13 @@
         <v>175</v>
       </c>
       <c r="C185" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D185" s="58">
         <v>11</v>
       </c>
       <c r="E185" s="58" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F185" s="59">
         <v>19.78</v>
@@ -7605,10 +7602,10 @@
         <v>83.076000000000008</v>
       </c>
       <c r="J185" s="61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K185" s="61" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="186" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -7623,7 +7620,7 @@
         <v>5</v>
       </c>
       <c r="E186" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F186" s="21">
         <v>12.5</v>
@@ -7661,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F187" s="12">
         <v>12.5</v>
@@ -7675,10 +7672,10 @@
         <v>30</v>
       </c>
       <c r="J187" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K187" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="188" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -7693,7 +7690,7 @@
         <v>13</v>
       </c>
       <c r="E188" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F188" s="21">
         <v>12.5</v>
@@ -7731,7 +7728,7 @@
         <v>126</v>
       </c>
       <c r="E189" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F189" s="21">
         <v>12.5</v>
@@ -7769,7 +7766,7 @@
         <v>127</v>
       </c>
       <c r="E190" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F190" s="21">
         <v>12.5</v>
@@ -7807,7 +7804,7 @@
         <v>128</v>
       </c>
       <c r="E191" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F191" s="12">
         <v>12.5</v>
@@ -7821,10 +7818,10 @@
         <v>30</v>
       </c>
       <c r="J191" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K191" s="9" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="192" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7839,7 +7836,7 @@
         <v>129</v>
       </c>
       <c r="E192" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F192" s="12">
         <v>12.5</v>
@@ -7853,10 +7850,10 @@
         <v>30</v>
       </c>
       <c r="J192" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K192" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="193" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -7871,7 +7868,7 @@
         <v>130</v>
       </c>
       <c r="E193" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F193" s="21">
         <v>12.5</v>
@@ -7903,13 +7900,13 @@
         <v>184</v>
       </c>
       <c r="C194" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D194" s="58">
         <v>12</v>
       </c>
       <c r="E194" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F194" s="59">
         <v>100.05</v>
@@ -7923,10 +7920,10 @@
         <v>420.21</v>
       </c>
       <c r="J194" s="61" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="K194" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="195" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7935,13 +7932,13 @@
         <v>185</v>
       </c>
       <c r="C195" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D195" s="58">
         <v>14</v>
       </c>
       <c r="E195" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F195" s="59">
         <v>27.66</v>
@@ -7955,10 +7952,10 @@
         <v>116.17200000000001</v>
       </c>
       <c r="J195" s="61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K195" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="196" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7967,13 +7964,13 @@
         <v>186</v>
       </c>
       <c r="C196" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D196" s="58">
         <v>15</v>
       </c>
       <c r="E196" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F196" s="59">
         <v>51.61</v>
@@ -7987,10 +7984,10 @@
         <v>216.762</v>
       </c>
       <c r="J196" s="61" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K196" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="197" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -7999,13 +7996,13 @@
         <v>187</v>
       </c>
       <c r="C197" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D197" s="58">
         <v>16</v>
       </c>
       <c r="E197" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F197" s="59">
         <v>19.260000000000002</v>
@@ -8019,10 +8016,10 @@
         <v>80.89200000000001</v>
       </c>
       <c r="J197" s="61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K197" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="198" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8031,13 +8028,13 @@
         <v>188</v>
       </c>
       <c r="C198" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D198" s="58">
         <v>17</v>
       </c>
       <c r="E198" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F198" s="59">
         <v>20.09</v>
@@ -8051,10 +8048,10 @@
         <v>84.378</v>
       </c>
       <c r="J198" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K198" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="199" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8063,13 +8060,13 @@
         <v>189</v>
       </c>
       <c r="C199" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D199" s="58">
         <v>18</v>
       </c>
       <c r="E199" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F199" s="59">
         <v>38.21</v>
@@ -8086,7 +8083,7 @@
         <v>26</v>
       </c>
       <c r="K199" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="200" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8095,13 +8092,13 @@
         <v>190</v>
       </c>
       <c r="C200" s="57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D200" s="58">
         <v>19</v>
       </c>
       <c r="E200" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F200" s="59">
         <v>23.54</v>
@@ -8115,10 +8112,10 @@
         <v>98.867999999999995</v>
       </c>
       <c r="J200" s="61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K200" s="61" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="201" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8127,13 +8124,13 @@
         <v>191</v>
       </c>
       <c r="C201" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D201" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E201" s="49" t="s">
         <v>79</v>
-      </c>
-      <c r="D201" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="E201" s="49" t="s">
-        <v>80</v>
       </c>
       <c r="F201" s="50">
         <v>50.36</v>
@@ -8147,10 +8144,10 @@
         <v>211.512</v>
       </c>
       <c r="J201" s="52" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K201" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="202" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8159,13 +8156,13 @@
         <v>192</v>
       </c>
       <c r="C202" s="48" t="s">
+        <v>78</v>
+      </c>
+      <c r="D202" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="E202" s="49" t="s">
         <v>79</v>
-      </c>
-      <c r="D202" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E202" s="49" t="s">
-        <v>80</v>
       </c>
       <c r="F202" s="50">
         <v>50.26</v>
@@ -8179,10 +8176,10 @@
         <v>211.09200000000001</v>
       </c>
       <c r="J202" s="52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K202" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="203" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -8191,13 +8188,13 @@
         <v>193</v>
       </c>
       <c r="C203" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="D203" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="E203" s="54" t="s">
         <v>79</v>
-      </c>
-      <c r="D203" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="E203" s="54" t="s">
-        <v>80</v>
       </c>
       <c r="F203" s="51">
         <v>54.14</v>
@@ -8211,10 +8208,10 @@
         <v>227.38800000000001</v>
       </c>
       <c r="J203" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K203" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L203" s="23">
         <f>+I203</f>
@@ -8229,13 +8226,13 @@
         <v>194</v>
       </c>
       <c r="C204" s="53" t="s">
+        <v>78</v>
+      </c>
+      <c r="D204" s="54" t="s">
+        <v>87</v>
+      </c>
+      <c r="E204" s="54" t="s">
         <v>79</v>
-      </c>
-      <c r="D204" s="54" t="s">
-        <v>88</v>
-      </c>
-      <c r="E204" s="54" t="s">
-        <v>80</v>
       </c>
       <c r="F204" s="51">
         <v>52.59</v>
@@ -8249,10 +8246,10 @@
         <v>220.87800000000001</v>
       </c>
       <c r="J204" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K204" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L204" s="23">
         <f>+I204</f>
@@ -8267,13 +8264,13 @@
         <v>195</v>
       </c>
       <c r="C205" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D205" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E205" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F205" s="49">
         <v>52.57</v>
@@ -8289,10 +8286,10 @@
         <v>220.79400000000001</v>
       </c>
       <c r="J205" s="52" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K205" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="206" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8301,13 +8298,13 @@
         <v>196</v>
       </c>
       <c r="C206" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D206" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E206" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F206" s="49">
         <v>100.66</v>
@@ -8323,10 +8320,10 @@
         <v>422.77199999999999</v>
       </c>
       <c r="J206" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K206" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="207" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8335,13 +8332,13 @@
         <v>197</v>
       </c>
       <c r="C207" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D207" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E207" s="49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F207" s="50">
         <v>46.95</v>
@@ -8355,10 +8352,10 @@
         <v>197.19000000000003</v>
       </c>
       <c r="J207" s="52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K207" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="208" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -8367,13 +8364,13 @@
         <v>198</v>
       </c>
       <c r="C208" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D208" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="E208" s="49" t="s">
         <v>84</v>
-      </c>
-      <c r="E208" s="49" t="s">
-        <v>85</v>
       </c>
       <c r="F208" s="50">
         <v>52.46</v>
@@ -8387,10 +8384,10 @@
         <v>220.33200000000002</v>
       </c>
       <c r="J208" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K208" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="209" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8399,13 +8396,13 @@
         <v>199</v>
       </c>
       <c r="C209" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D209" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E209" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F209" s="50">
         <v>44.96</v>
@@ -8419,10 +8416,10 @@
         <v>188.83200000000002</v>
       </c>
       <c r="J209" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K209" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="210" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8431,13 +8428,13 @@
         <v>200</v>
       </c>
       <c r="C210" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D210" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E210" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F210" s="50">
         <v>52.56</v>
@@ -8451,10 +8448,10 @@
         <v>220.75200000000001</v>
       </c>
       <c r="J210" s="52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K210" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="211" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8463,13 +8460,13 @@
         <v>201</v>
       </c>
       <c r="C211" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D211" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E211" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F211" s="50">
         <v>51.59</v>
@@ -8483,10 +8480,10 @@
         <v>216.67800000000003</v>
       </c>
       <c r="J211" s="52" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K211" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="212" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8495,13 +8492,13 @@
         <v>202</v>
       </c>
       <c r="C212" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D212" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E212" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F212" s="50">
         <v>40.47</v>
@@ -8515,10 +8512,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J212" s="52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K212" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="213" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8527,13 +8524,13 @@
         <v>203</v>
       </c>
       <c r="C213" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D213" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E213" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F213" s="50">
         <v>40.47</v>
@@ -8547,10 +8544,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J213" s="52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K213" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="214" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8559,13 +8556,13 @@
         <v>204</v>
       </c>
       <c r="C214" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D214" s="49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E214" s="49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F214" s="50">
         <v>52.88</v>
@@ -8579,10 +8576,10 @@
         <v>222.09600000000003</v>
       </c>
       <c r="J214" s="52" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K214" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="215" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8591,13 +8588,13 @@
         <v>205</v>
       </c>
       <c r="C215" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D215" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E215" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F215" s="50">
         <v>52.46</v>
@@ -8611,10 +8608,10 @@
         <v>220.33200000000002</v>
       </c>
       <c r="J215" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K215" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="216" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8623,13 +8620,13 @@
         <v>206</v>
       </c>
       <c r="C216" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D216" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E216" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F216" s="50">
         <v>44.96</v>
@@ -8643,10 +8640,10 @@
         <v>188.83200000000002</v>
       </c>
       <c r="J216" s="52" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K216" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="217" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8655,13 +8652,13 @@
         <v>207</v>
       </c>
       <c r="C217" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D217" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E217" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F217" s="50">
         <v>52.56</v>
@@ -8675,10 +8672,10 @@
         <v>220.75200000000001</v>
       </c>
       <c r="J217" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K217" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="218" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8687,13 +8684,13 @@
         <v>208</v>
       </c>
       <c r="C218" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D218" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E218" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F218" s="50">
         <v>51.59</v>
@@ -8707,10 +8704,10 @@
         <v>216.67800000000003</v>
       </c>
       <c r="J218" s="52" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K218" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="219" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8719,13 +8716,13 @@
         <v>209</v>
       </c>
       <c r="C219" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D219" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E219" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F219" s="50">
         <v>40.47</v>
@@ -8739,10 +8736,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J219" s="52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K219" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="220" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8751,13 +8748,13 @@
         <v>210</v>
       </c>
       <c r="C220" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D220" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E220" s="49" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F220" s="50">
         <v>40.47</v>
@@ -8771,10 +8768,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J220" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K220" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="221" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8783,13 +8780,13 @@
         <v>211</v>
       </c>
       <c r="C221" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D221" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="E221" s="49" t="s">
         <v>93</v>
-      </c>
-      <c r="E221" s="49" t="s">
-        <v>94</v>
       </c>
       <c r="F221" s="50">
         <v>52.88</v>
@@ -8803,10 +8800,10 @@
         <v>222.09600000000003</v>
       </c>
       <c r="J221" s="52" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K221" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="222" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8815,13 +8812,13 @@
         <v>212</v>
       </c>
       <c r="C222" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D222" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E222" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F222" s="50">
         <v>52.46</v>
@@ -8835,10 +8832,10 @@
         <v>220.33200000000002</v>
       </c>
       <c r="J222" s="52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K222" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="223" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8847,13 +8844,13 @@
         <v>213</v>
       </c>
       <c r="C223" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D223" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E223" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F223" s="50">
         <v>44.96</v>
@@ -8867,10 +8864,10 @@
         <v>188.83200000000002</v>
       </c>
       <c r="J223" s="52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K223" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="224" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8879,13 +8876,13 @@
         <v>214</v>
       </c>
       <c r="C224" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D224" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E224" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F224" s="50">
         <v>52.56</v>
@@ -8899,10 +8896,10 @@
         <v>220.75200000000001</v>
       </c>
       <c r="J224" s="52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K224" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="225" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8911,13 +8908,13 @@
         <v>215</v>
       </c>
       <c r="C225" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D225" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E225" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F225" s="50">
         <v>51.59</v>
@@ -8931,10 +8928,10 @@
         <v>216.67800000000003</v>
       </c>
       <c r="J225" s="52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K225" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="226" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8943,13 +8940,13 @@
         <v>216</v>
       </c>
       <c r="C226" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D226" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E226" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F226" s="50">
         <v>40.47</v>
@@ -8963,10 +8960,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J226" s="52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K226" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="227" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -8975,13 +8972,13 @@
         <v>217</v>
       </c>
       <c r="C227" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D227" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E227" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F227" s="50">
         <v>40.47</v>
@@ -8995,10 +8992,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J227" s="52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K227" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="228" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9007,13 +9004,13 @@
         <v>218</v>
       </c>
       <c r="C228" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D228" s="49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E228" s="49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F228" s="50">
         <v>52.88</v>
@@ -9027,10 +9024,10 @@
         <v>222.09600000000003</v>
       </c>
       <c r="J228" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K228" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="229" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9039,13 +9036,13 @@
         <v>219</v>
       </c>
       <c r="C229" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D229" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E229" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F229" s="50">
         <v>52.46</v>
@@ -9059,10 +9056,10 @@
         <v>220.33200000000002</v>
       </c>
       <c r="J229" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K229" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="230" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9071,13 +9068,13 @@
         <v>220</v>
       </c>
       <c r="C230" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D230" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E230" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F230" s="50">
         <v>44.96</v>
@@ -9091,10 +9088,10 @@
         <v>188.83200000000002</v>
       </c>
       <c r="J230" s="52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K230" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="231" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9103,13 +9100,13 @@
         <v>221</v>
       </c>
       <c r="C231" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D231" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E231" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F231" s="50">
         <v>52.56</v>
@@ -9123,10 +9120,10 @@
         <v>220.75200000000001</v>
       </c>
       <c r="J231" s="52" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K231" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="232" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9135,13 +9132,13 @@
         <v>222</v>
       </c>
       <c r="C232" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D232" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E232" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F232" s="50">
         <v>51.59</v>
@@ -9155,10 +9152,10 @@
         <v>216.67800000000003</v>
       </c>
       <c r="J232" s="52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K232" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="233" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9167,13 +9164,13 @@
         <v>223</v>
       </c>
       <c r="C233" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D233" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E233" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F233" s="50">
         <v>40.47</v>
@@ -9187,10 +9184,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J233" s="52" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K233" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="234" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9199,13 +9196,13 @@
         <v>224</v>
       </c>
       <c r="C234" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D234" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E234" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F234" s="50">
         <v>40.47</v>
@@ -9219,10 +9216,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J234" s="52" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K234" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="235" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9231,13 +9228,13 @@
         <v>225</v>
       </c>
       <c r="C235" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D235" s="49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E235" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F235" s="50">
         <v>52.88</v>
@@ -9251,10 +9248,10 @@
         <v>222.09600000000003</v>
       </c>
       <c r="J235" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K235" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="236" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9263,13 +9260,13 @@
         <v>226</v>
       </c>
       <c r="C236" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D236" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E236" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F236" s="50">
         <v>52.46</v>
@@ -9283,10 +9280,10 @@
         <v>220.33200000000002</v>
       </c>
       <c r="J236" s="52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K236" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="237" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9295,13 +9292,13 @@
         <v>227</v>
       </c>
       <c r="C237" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D237" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E237" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F237" s="50">
         <v>44.96</v>
@@ -9315,10 +9312,10 @@
         <v>188.83200000000002</v>
       </c>
       <c r="J237" s="52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K237" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="238" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9327,13 +9324,13 @@
         <v>228</v>
       </c>
       <c r="C238" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D238" s="49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E238" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F238" s="50">
         <v>52.56</v>
@@ -9347,10 +9344,10 @@
         <v>220.75200000000001</v>
       </c>
       <c r="J238" s="52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K238" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="239" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9359,13 +9356,13 @@
         <v>229</v>
       </c>
       <c r="C239" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D239" s="49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E239" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F239" s="50">
         <v>51.59</v>
@@ -9379,10 +9376,10 @@
         <v>216.67800000000003</v>
       </c>
       <c r="J239" s="52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K239" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="240" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9391,13 +9388,13 @@
         <v>230</v>
       </c>
       <c r="C240" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D240" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E240" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F240" s="50">
         <v>40.47</v>
@@ -9411,10 +9408,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J240" s="52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K240" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="241" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9423,13 +9420,13 @@
         <v>231</v>
       </c>
       <c r="C241" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D241" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E241" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F241" s="50">
         <v>40.47</v>
@@ -9443,10 +9440,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J241" s="52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K241" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="242" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9455,13 +9452,13 @@
         <v>232</v>
       </c>
       <c r="C242" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D242" s="49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E242" s="49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F242" s="50">
         <v>52.88</v>
@@ -9475,10 +9472,10 @@
         <v>222.09600000000003</v>
       </c>
       <c r="J242" s="52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K242" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="243" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9487,13 +9484,13 @@
         <v>233</v>
       </c>
       <c r="C243" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D243" s="49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E243" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F243" s="50">
         <v>52.46</v>
@@ -9507,10 +9504,10 @@
         <v>220.33200000000002</v>
       </c>
       <c r="J243" s="52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K243" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="244" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9519,13 +9516,13 @@
         <v>234</v>
       </c>
       <c r="C244" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D244" s="49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E244" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F244" s="50">
         <v>42.54</v>
@@ -9539,10 +9536,10 @@
         <v>178.66800000000001</v>
       </c>
       <c r="J244" s="52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K244" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="245" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
@@ -9551,13 +9548,13 @@
         <v>235</v>
       </c>
       <c r="C245" s="53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D245" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E245" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F245" s="51">
         <v>52.56</v>
@@ -9571,10 +9568,10 @@
         <v>220.75200000000001</v>
       </c>
       <c r="J245" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K245" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L245" s="23">
         <f>+I245</f>
@@ -9589,13 +9586,13 @@
         <v>236</v>
       </c>
       <c r="C246" s="53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D246" s="54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E246" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F246" s="51">
         <v>51.59</v>
@@ -9609,10 +9606,10 @@
         <v>216.67800000000003</v>
       </c>
       <c r="J246" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K246" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L246" s="23">
         <f>+I246</f>
@@ -9627,13 +9624,13 @@
         <v>237</v>
       </c>
       <c r="C247" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D247" s="49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E247" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F247" s="50">
         <v>40.47</v>
@@ -9647,10 +9644,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J247" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K247" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="248" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9659,13 +9656,13 @@
         <v>238</v>
       </c>
       <c r="C248" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D248" s="49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E248" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F248" s="50">
         <v>40.47</v>
@@ -9679,10 +9676,10 @@
         <v>169.97399999999999</v>
       </c>
       <c r="J248" s="52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K248" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="249" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9691,13 +9688,13 @@
         <v>239</v>
       </c>
       <c r="C249" s="48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D249" s="49" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E249" s="49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F249" s="50">
         <v>52.88</v>
@@ -9711,10 +9708,10 @@
         <v>222.09600000000003</v>
       </c>
       <c r="J249" s="52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K249" s="52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="250" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9723,13 +9720,13 @@
         <v>240</v>
       </c>
       <c r="C250" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D250" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="E250" s="44" t="s">
         <v>112</v>
-      </c>
-      <c r="D250" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="E250" s="44" t="s">
-        <v>113</v>
       </c>
       <c r="F250" s="45">
         <v>100.64</v>
@@ -9743,10 +9740,10 @@
         <v>241.536</v>
       </c>
       <c r="J250" s="42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K250" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="251" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9755,13 +9752,13 @@
         <v>241</v>
       </c>
       <c r="C251" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D251" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E251" s="44" t="s">
         <v>112</v>
-      </c>
-      <c r="D251" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="E251" s="44" t="s">
-        <v>113</v>
       </c>
       <c r="F251" s="45">
         <v>100.63</v>
@@ -9775,10 +9772,10 @@
         <v>241.51199999999997</v>
       </c>
       <c r="J251" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K251" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="252" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9787,13 +9784,13 @@
         <v>242</v>
       </c>
       <c r="C252" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D252" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="E252" s="44" t="s">
         <v>112</v>
-      </c>
-      <c r="D252" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="E252" s="44" t="s">
-        <v>113</v>
       </c>
       <c r="F252" s="45">
         <v>89.28</v>
@@ -9807,10 +9804,10 @@
         <v>214.27199999999999</v>
       </c>
       <c r="J252" s="42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K252" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="253" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9819,13 +9816,13 @@
         <v>243</v>
       </c>
       <c r="C253" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="D253" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="E253" s="44" t="s">
         <v>112</v>
-      </c>
-      <c r="D253" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="E253" s="44" t="s">
-        <v>113</v>
       </c>
       <c r="F253" s="45">
         <v>89.22</v>
@@ -9839,10 +9836,10 @@
         <v>214.12799999999999</v>
       </c>
       <c r="J253" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K253" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="254" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9851,13 +9848,13 @@
         <v>244</v>
       </c>
       <c r="C254" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D254" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E254" s="44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F254" s="45">
         <v>100.46</v>
@@ -9871,10 +9868,10 @@
         <v>241.10399999999998</v>
       </c>
       <c r="J254" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K254" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="255" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9883,13 +9880,13 @@
         <v>245</v>
       </c>
       <c r="C255" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D255" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E255" s="44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F255" s="45">
         <v>100.46</v>
@@ -9903,10 +9900,10 @@
         <v>241.10399999999998</v>
       </c>
       <c r="J255" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K255" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="256" spans="2:14" ht="18.75" x14ac:dyDescent="0.25">
@@ -9915,13 +9912,13 @@
         <v>246</v>
       </c>
       <c r="C256" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D256" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E256" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F256" s="45">
         <v>91.09</v>
@@ -9938,7 +9935,7 @@
         <v>28</v>
       </c>
       <c r="K256" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="257" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9947,13 +9944,13 @@
         <v>247</v>
       </c>
       <c r="C257" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D257" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E257" s="44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F257" s="45">
         <v>91.09</v>
@@ -9967,10 +9964,10 @@
         <v>218.61600000000001</v>
       </c>
       <c r="J257" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K257" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="258" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -9979,13 +9976,13 @@
         <v>248</v>
       </c>
       <c r="C258" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D258" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E258" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F258" s="45">
         <v>154.03</v>
@@ -10002,7 +9999,7 @@
         <v>18</v>
       </c>
       <c r="K258" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="259" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10011,13 +10008,13 @@
         <v>249</v>
       </c>
       <c r="C259" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D259" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E259" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F259" s="45">
         <v>153.94999999999999</v>
@@ -10031,10 +10028,10 @@
         <v>369.47999999999996</v>
       </c>
       <c r="J259" s="42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K259" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="260" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10043,13 +10040,13 @@
         <v>250</v>
       </c>
       <c r="C260" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D260" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E260" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F260" s="45">
         <v>42.07</v>
@@ -10063,10 +10060,10 @@
         <v>100.968</v>
       </c>
       <c r="J260" s="42" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K260" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="261" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10075,13 +10072,13 @@
         <v>251</v>
       </c>
       <c r="C261" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D261" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E261" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F261" s="45">
         <v>41.94</v>
@@ -10095,10 +10092,10 @@
         <v>100.65599999999999</v>
       </c>
       <c r="J261" s="42" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K261" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="262" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10107,13 +10104,13 @@
         <v>252</v>
       </c>
       <c r="C262" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D262" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E262" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F262" s="45">
         <v>154.03</v>
@@ -10127,10 +10124,10 @@
         <v>369.67199999999997</v>
       </c>
       <c r="J262" s="42" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K262" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="263" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10139,13 +10136,13 @@
         <v>253</v>
       </c>
       <c r="C263" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D263" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E263" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F263" s="45">
         <v>153.94999999999999</v>
@@ -10159,10 +10156,10 @@
         <v>369.47999999999996</v>
       </c>
       <c r="J263" s="42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K263" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="264" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10171,13 +10168,13 @@
         <v>254</v>
       </c>
       <c r="C264" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D264" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E264" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F264" s="45">
         <v>42.07</v>
@@ -10194,7 +10191,7 @@
         <v>21</v>
       </c>
       <c r="K264" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="265" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10203,13 +10200,13 @@
         <v>255</v>
       </c>
       <c r="C265" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D265" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E265" s="44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F265" s="45">
         <v>41.94</v>
@@ -10223,10 +10220,10 @@
         <v>100.65599999999999</v>
       </c>
       <c r="J265" s="42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K265" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="266" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10235,13 +10232,13 @@
         <v>256</v>
       </c>
       <c r="C266" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D266" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E266" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F266" s="45">
         <v>153.87</v>
@@ -10255,10 +10252,10 @@
         <v>369.28800000000001</v>
       </c>
       <c r="J266" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K266" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="267" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10267,13 +10264,13 @@
         <v>257</v>
       </c>
       <c r="C267" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D267" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E267" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F267" s="45">
         <v>147.97</v>
@@ -10287,10 +10284,10 @@
         <v>355.12799999999999</v>
       </c>
       <c r="J267" s="42" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K267" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="268" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10299,13 +10296,13 @@
         <v>258</v>
       </c>
       <c r="C268" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D268" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E268" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F268" s="45">
         <v>47.92</v>
@@ -10319,10 +10316,10 @@
         <v>115.008</v>
       </c>
       <c r="J268" s="42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K268" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="269" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10331,13 +10328,13 @@
         <v>259</v>
       </c>
       <c r="C269" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D269" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E269" s="44" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F269" s="45">
         <v>41.95</v>
@@ -10351,10 +10348,10 @@
         <v>100.68</v>
       </c>
       <c r="J269" s="42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K269" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="270" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10363,13 +10360,13 @@
         <v>260</v>
       </c>
       <c r="C270" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D270" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E270" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F270" s="45">
         <v>154.03</v>
@@ -10386,7 +10383,7 @@
         <v>26</v>
       </c>
       <c r="K270" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="271" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10395,13 +10392,13 @@
         <v>261</v>
       </c>
       <c r="C271" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D271" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E271" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F271" s="45">
         <v>153.94999999999999</v>
@@ -10415,10 +10412,10 @@
         <v>369.47999999999996</v>
       </c>
       <c r="J271" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K271" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="272" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10427,13 +10424,13 @@
         <v>262</v>
       </c>
       <c r="C272" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D272" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E272" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F272" s="45">
         <v>42.07</v>
@@ -10447,10 +10444,10 @@
         <v>100.968</v>
       </c>
       <c r="J272" s="42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K272" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="273" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10459,13 +10456,13 @@
         <v>263</v>
       </c>
       <c r="C273" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D273" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E273" s="44" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F273" s="45">
         <v>41.94</v>
@@ -10479,10 +10476,10 @@
         <v>100.65599999999999</v>
       </c>
       <c r="J273" s="42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K273" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="274" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10491,13 +10488,13 @@
         <v>264</v>
       </c>
       <c r="C274" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D274" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E274" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F274" s="45">
         <v>153.87</v>
@@ -10511,10 +10508,10 @@
         <v>369.28800000000001</v>
       </c>
       <c r="J274" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K274" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="275" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10523,13 +10520,13 @@
         <v>265</v>
       </c>
       <c r="C275" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D275" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E275" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F275" s="45">
         <v>147.97</v>
@@ -10543,10 +10540,10 @@
         <v>355.12799999999999</v>
       </c>
       <c r="J275" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K275" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="276" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10555,13 +10552,13 @@
         <v>266</v>
       </c>
       <c r="C276" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D276" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E276" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F276" s="45">
         <v>47.92</v>
@@ -10575,10 +10572,10 @@
         <v>115.008</v>
       </c>
       <c r="J276" s="42" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K276" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="277" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10587,13 +10584,13 @@
         <v>267</v>
       </c>
       <c r="C277" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D277" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E277" s="44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F277" s="45">
         <v>41.95</v>
@@ -10607,10 +10604,10 @@
         <v>100.68</v>
       </c>
       <c r="J277" s="42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K277" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="278" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10619,13 +10616,13 @@
         <v>268</v>
       </c>
       <c r="C278" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D278" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E278" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F278" s="45">
         <v>153.87</v>
@@ -10639,10 +10636,10 @@
         <v>369.28800000000001</v>
       </c>
       <c r="J278" s="42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K278" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="279" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10651,13 +10648,13 @@
         <v>269</v>
       </c>
       <c r="C279" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D279" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E279" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F279" s="45">
         <v>147.97</v>
@@ -10674,7 +10671,7 @@
         <v>22</v>
       </c>
       <c r="K279" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="280" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10683,13 +10680,13 @@
         <v>270</v>
       </c>
       <c r="C280" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D280" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E280" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F280" s="45">
         <v>47.92</v>
@@ -10703,10 +10700,10 @@
         <v>115.008</v>
       </c>
       <c r="J280" s="42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K280" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="281" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10715,13 +10712,13 @@
         <v>271</v>
       </c>
       <c r="C281" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D281" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E281" s="44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F281" s="45">
         <v>41.95</v>
@@ -10735,10 +10732,10 @@
         <v>100.68</v>
       </c>
       <c r="J281" s="42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K281" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="282" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10747,13 +10744,13 @@
         <v>272</v>
       </c>
       <c r="C282" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D282" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E282" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F282" s="45">
         <v>148.04</v>
@@ -10767,10 +10764,10 @@
         <v>355.29599999999999</v>
       </c>
       <c r="J282" s="42" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K282" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="283" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10779,13 +10776,13 @@
         <v>273</v>
       </c>
       <c r="C283" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D283" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E283" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F283" s="45">
         <v>147.97</v>
@@ -10799,10 +10796,10 @@
         <v>355.12799999999999</v>
       </c>
       <c r="J283" s="42" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K283" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="284" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10811,13 +10808,13 @@
         <v>274</v>
       </c>
       <c r="C284" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D284" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E284" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F284" s="45">
         <v>47.92</v>
@@ -10831,10 +10828,10 @@
         <v>115.008</v>
       </c>
       <c r="J284" s="42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K284" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="285" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10843,13 +10840,13 @@
         <v>275</v>
       </c>
       <c r="C285" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D285" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E285" s="44" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F285" s="45">
         <v>47.78</v>
@@ -10863,10 +10860,10 @@
         <v>114.672</v>
       </c>
       <c r="J285" s="42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K285" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="286" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10875,13 +10872,13 @@
         <v>276</v>
       </c>
       <c r="C286" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D286" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E286" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F286" s="45">
         <v>153.87</v>
@@ -10895,10 +10892,10 @@
         <v>369.28800000000001</v>
       </c>
       <c r="J286" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K286" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="287" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10907,13 +10904,13 @@
         <v>277</v>
       </c>
       <c r="C287" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D287" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E287" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F287" s="45">
         <v>147.97</v>
@@ -10930,7 +10927,7 @@
         <v>20</v>
       </c>
       <c r="K287" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="288" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10939,13 +10936,13 @@
         <v>278</v>
       </c>
       <c r="C288" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D288" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E288" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F288" s="45">
         <v>47.92</v>
@@ -10959,10 +10956,10 @@
         <v>115.008</v>
       </c>
       <c r="J288" s="42" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="K288" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="289" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -10971,13 +10968,13 @@
         <v>279</v>
       </c>
       <c r="C289" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D289" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E289" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F289" s="45">
         <v>41.95</v>
@@ -10991,10 +10988,10 @@
         <v>100.68</v>
       </c>
       <c r="J289" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K289" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="290" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11003,13 +11000,13 @@
         <v>280</v>
       </c>
       <c r="C290" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D290" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E290" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F290" s="45">
         <v>148.04</v>
@@ -11023,10 +11020,10 @@
         <v>355.29599999999999</v>
       </c>
       <c r="J290" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K290" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="291" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11035,13 +11032,13 @@
         <v>281</v>
       </c>
       <c r="C291" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D291" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E291" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F291" s="45">
         <v>147.97</v>
@@ -11058,7 +11055,7 @@
         <v>17</v>
       </c>
       <c r="K291" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="292" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11067,13 +11064,13 @@
         <v>282</v>
       </c>
       <c r="C292" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D292" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E292" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F292" s="45">
         <v>47.92</v>
@@ -11087,10 +11084,10 @@
         <v>115.008</v>
       </c>
       <c r="J292" s="42" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="K292" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="293" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11099,13 +11096,13 @@
         <v>283</v>
       </c>
       <c r="C293" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D293" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E293" s="44" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F293" s="45">
         <v>47.78</v>
@@ -11119,10 +11116,10 @@
         <v>114.672</v>
       </c>
       <c r="J293" s="42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K293" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="294" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11131,13 +11128,13 @@
         <v>284</v>
       </c>
       <c r="C294" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D294" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E294" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F294" s="45">
         <v>153.87</v>
@@ -11151,10 +11148,10 @@
         <v>369.28800000000001</v>
       </c>
       <c r="J294" s="42" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="K294" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="295" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11163,13 +11160,13 @@
         <v>285</v>
       </c>
       <c r="C295" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D295" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E295" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F295" s="45">
         <v>147.97</v>
@@ -11186,7 +11183,7 @@
         <v>19</v>
       </c>
       <c r="K295" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="296" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11195,13 +11192,13 @@
         <v>286</v>
       </c>
       <c r="C296" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D296" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E296" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F296" s="45">
         <v>47.92</v>
@@ -11215,10 +11212,10 @@
         <v>115.008</v>
       </c>
       <c r="J296" s="42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K296" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="297" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11227,13 +11224,13 @@
         <v>287</v>
       </c>
       <c r="C297" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D297" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E297" s="44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F297" s="45">
         <v>41.95</v>
@@ -11247,10 +11244,10 @@
         <v>100.68</v>
       </c>
       <c r="J297" s="42" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="K297" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="298" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11259,13 +11256,13 @@
         <v>288</v>
       </c>
       <c r="C298" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D298" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E298" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F298" s="45">
         <v>148.04</v>
@@ -11279,10 +11276,10 @@
         <v>355.29599999999999</v>
       </c>
       <c r="J298" s="42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K298" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="299" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11291,13 +11288,13 @@
         <v>289</v>
       </c>
       <c r="C299" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D299" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E299" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F299" s="45">
         <v>147.97</v>
@@ -11311,10 +11308,10 @@
         <v>355.12799999999999</v>
       </c>
       <c r="J299" s="42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K299" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="300" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11323,13 +11320,13 @@
         <v>290</v>
       </c>
       <c r="C300" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D300" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E300" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F300" s="45">
         <v>47.92</v>
@@ -11343,10 +11340,10 @@
         <v>115.008</v>
       </c>
       <c r="J300" s="42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K300" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="301" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11355,13 +11352,13 @@
         <v>291</v>
       </c>
       <c r="C301" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D301" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E301" s="44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F301" s="45">
         <v>47.78</v>
@@ -11375,10 +11372,10 @@
         <v>114.672</v>
       </c>
       <c r="J301" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K301" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="302" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11387,13 +11384,13 @@
         <v>292</v>
       </c>
       <c r="C302" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D302" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E302" s="44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F302" s="45">
         <v>154.01</v>
@@ -11407,10 +11404,10 @@
         <v>369.62399999999997</v>
       </c>
       <c r="J302" s="42" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K302" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="303" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11419,13 +11416,13 @@
         <v>293</v>
       </c>
       <c r="C303" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D303" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E303" s="44" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F303" s="45">
         <v>153.93</v>
@@ -11439,10 +11436,10 @@
         <v>369.43200000000002</v>
       </c>
       <c r="J303" s="42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K303" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="304" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11451,13 +11448,13 @@
         <v>294</v>
       </c>
       <c r="C304" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D304" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E304" s="44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F304" s="45">
         <v>42.05</v>
@@ -11471,10 +11468,10 @@
         <v>100.91999999999999</v>
       </c>
       <c r="J304" s="42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K304" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="305" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11483,13 +11480,13 @@
         <v>295</v>
       </c>
       <c r="C305" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D305" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E305" s="44" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F305" s="45">
         <v>41.92</v>
@@ -11503,10 +11500,10 @@
         <v>100.608</v>
       </c>
       <c r="J305" s="42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K305" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="306" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11515,13 +11512,13 @@
         <v>296</v>
       </c>
       <c r="C306" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D306" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E306" s="44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F306" s="45">
         <v>148.04</v>
@@ -11535,10 +11532,10 @@
         <v>355.29599999999999</v>
       </c>
       <c r="J306" s="42" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K306" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="307" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11547,13 +11544,13 @@
         <v>297</v>
       </c>
       <c r="C307" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D307" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E307" s="44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F307" s="45">
         <v>147.97</v>
@@ -11567,10 +11564,10 @@
         <v>355.12799999999999</v>
       </c>
       <c r="J307" s="42" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K307" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="308" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11579,13 +11576,13 @@
         <v>298</v>
       </c>
       <c r="C308" s="43" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D308" s="44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E308" s="44" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F308" s="44">
         <v>47.92</v>
@@ -11599,10 +11596,10 @@
         <v>115.008</v>
       </c>
       <c r="J308" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K308" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="309" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11611,13 +11608,13 @@
         <v>299</v>
       </c>
       <c r="C309" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D309" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E309" s="44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F309" s="45">
         <v>47.78</v>
@@ -11631,10 +11628,10 @@
         <v>114.672</v>
       </c>
       <c r="J309" s="42" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K309" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="310" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11643,13 +11640,13 @@
         <v>300</v>
       </c>
       <c r="C310" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D310" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E310" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F310" s="45">
         <v>100.46</v>
@@ -11663,10 +11660,10 @@
         <v>241.10399999999998</v>
       </c>
       <c r="J310" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K310" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="311" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11675,13 +11672,13 @@
         <v>301</v>
       </c>
       <c r="C311" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D311" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E311" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F311" s="45">
         <v>100.46</v>
@@ -11695,10 +11692,10 @@
         <v>241.10399999999998</v>
       </c>
       <c r="J311" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K311" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="312" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11707,13 +11704,13 @@
         <v>302</v>
       </c>
       <c r="C312" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D312" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E312" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F312" s="45">
         <v>91.09</v>
@@ -11727,10 +11724,10 @@
         <v>218.61600000000001</v>
       </c>
       <c r="J312" s="42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K312" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="313" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11739,13 +11736,13 @@
         <v>303</v>
       </c>
       <c r="C313" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D313" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E313" s="44" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F313" s="45">
         <v>91.09</v>
@@ -11759,10 +11756,10 @@
         <v>218.61600000000001</v>
       </c>
       <c r="J313" s="42" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K313" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="314" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11771,13 +11768,13 @@
         <v>304</v>
       </c>
       <c r="C314" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D314" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E314" s="44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F314" s="45">
         <v>210.88</v>
@@ -11791,10 +11788,10 @@
         <v>506.11199999999997</v>
       </c>
       <c r="J314" s="42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K314" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="315" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11803,13 +11800,13 @@
         <v>305</v>
       </c>
       <c r="C315" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D315" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E315" s="44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F315" s="45">
         <v>91.19</v>
@@ -11823,10 +11820,10 @@
         <v>218.85599999999999</v>
       </c>
       <c r="J315" s="42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K315" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="316" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11835,13 +11832,13 @@
         <v>306</v>
       </c>
       <c r="C316" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D316" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E316" s="44" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F316" s="45">
         <v>90.81</v>
@@ -11855,10 +11852,10 @@
         <v>217.94399999999999</v>
       </c>
       <c r="J316" s="42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K316" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="317" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11867,13 +11864,13 @@
         <v>307</v>
       </c>
       <c r="C317" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D317" s="44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E317" s="44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F317" s="45">
         <v>260.95999999999998</v>
@@ -11887,10 +11884,10 @@
         <v>626.30399999999997</v>
       </c>
       <c r="J317" s="42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K317" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="318" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11899,13 +11896,13 @@
         <v>308</v>
       </c>
       <c r="C318" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D318" s="44" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E318" s="44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F318" s="45">
         <v>254.76</v>
@@ -11922,7 +11919,7 @@
         <v>23</v>
       </c>
       <c r="K318" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="319" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
@@ -11931,13 +11928,13 @@
         <v>309</v>
       </c>
       <c r="C319" s="43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D319" s="44">
         <v>30</v>
       </c>
       <c r="E319" s="44" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F319" s="45">
         <v>253.93</v>
@@ -11951,16 +11948,16 @@
         <v>609.43200000000002</v>
       </c>
       <c r="J319" s="42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K319" s="42" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B320" s="26"/>
       <c r="C320" s="63" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D320" s="63"/>
       <c r="E320" s="63"/>
@@ -11977,7 +11974,7 @@
     <row r="321" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B321" s="26"/>
       <c r="C321" s="63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D321" s="63"/>
       <c r="E321" s="63"/>
